--- a/public/templates/000_pm_suite/02_프로젝트 개발/03_분석/02_환경분석/프로젝트명_콘텐츠수급리스트_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/02_프로젝트 개발/03_분석/02_환경분석/프로젝트명_콘텐츠수급리스트_V1.0_20230530.xlsx
@@ -520,14 +520,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-33-C] SyncGuard AI 구축 필수 도메인 콘텐츠 및 학습·검증 데이터 수급 관리대장 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-33-C] SyncFlow AI 구축 필수 도메인 콘텐츠 및 학습·검증 데이터 수급 관리대장 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>법령 고시, 사내 심의 가이드라인, 100대 금지어 사전, 골든셋 50문항 및 전성분 샘플 수급 완료 현황 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+          <t>법령 고시, 사내 검증 가이드라인, 100대 독소조항 사전, 골든셋 50문항 및 자재BOM 샘플 수급 완료 현황 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 관리 가이드라인 최신본 및 고시 전문</t>
+          <t>공정위·표준원 구매계약·기술규격 관리 가이드라인 최신본 및 고시 전문</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀</t>
+          <t>규제검증팀</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>한빛글로벌 사내 표시·광고 금지/주의/허용 표현 마스터 사전</t>
+          <t>한빛글로벌 사내 계약·기술규격 금지/주의/허용 표현 마스터 사전</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>규제심의팀</t>
+          <t>규제검증팀</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>과거 3개년 실제 심의 반려·수정 사례 및 표준 골든셋 50문항</t>
+          <t>과거 3개년 실제 검토 반려·수정 사례 및 표준 골든셋 50문항</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀</t>
+          <t>규제검증팀</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>4대 주력 브랜드(루미에르·벨르코어·아쿠아퓨어·더마쉴드) 상세페이지 시안</t>
+          <t>4대 주력 사업본부(전장시스템·배터리모듈·배터리모듈본부·스마트팩토리본부) 기술시방서 계약·도서</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>럭셔리마케팅팀</t>
+          <t>핵심모듈구매조달팀</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ProductLab 전성분 마스터 및 품목별 배합비 스키마 정의서·샘플 덤프</t>
+          <t>PLM-Nexus 자재BOM 마스터 및 품목별 조성비 스키마 정의서·샘플 덤프</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>한빛글로벌 공식 CI 로고, 브랜드 전용 웹폰트 및 UI 컬러 가이드</t>
+          <t>한빛글로벌 공식 CI 로고, 사업본부 전용 웹폰트 및 UI 컬러 가이드</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>브랜드디자인팀</t>
+          <t>사업본부디자인팀</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
